--- a/DataTables/DetailText/剧情/018库房失火.xlsx
+++ b/DataTables/DetailText/剧情/018库房失火.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D948C50-B1B4-4111-B82A-C56DF0C812F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85CCDC3-898A-4924-A752-CD5ACED7FFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -192,6 +192,35 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>这火烧的蹊跷。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>那边抬出来一个人。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>……是杨善泉。</t>
+    <rPh sb="2" eb="3">
+      <t>ゼ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ゼン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イズミ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>018</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>017_02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
       <t>res://Assets/Background/0</t>
     </r>
@@ -203,7 +232,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>19</t>
+      <t>18</t>
     </r>
     <r>
       <rPr>
@@ -223,7 +252,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>019</t>
+      <t>018</t>
     </r>
     <r>
       <rPr>
@@ -235,35 +264,6 @@
       </rPr>
       <t>.png</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>这火烧的蹊跷。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>那边抬出来一个人。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>……是杨善泉。</t>
-    <rPh sb="2" eb="3">
-      <t>ゼ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>イズミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>018</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>017_02</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -809,7 +809,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>29</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1026,10 +1026,10 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>37</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1049,7 +1049,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1069,7 +1069,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/018库房失火.xlsx
+++ b/DataTables/DetailText/剧情/018库房失火.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85CCDC3-898A-4924-A752-CD5ACED7FFA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9A95A2-022E-4AFE-8364-14B0ECFF89B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -184,15 +184,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>少掌柜的，惠民药局的药料库期货啦。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>走，去帮忙。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>这火烧的蹊跷。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -264,6 +256,14 @@
       </rPr>
       <t>.png</t>
     </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少掌柜的，惠民药局的药料库起火啦。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>这火烧得蹊跷。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -809,7 +809,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>29</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -987,7 +987,7 @@
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="19" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1007,7 +1007,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1026,10 +1026,10 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>42</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1049,7 +1049,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1069,7 +1069,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/018库房失火.xlsx
+++ b/DataTables/DetailText/剧情/018库房失火.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9A95A2-022E-4AFE-8364-14B0ECFF89B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84753520-9A8B-449C-8B9E-BF0873CB3701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -147,10 +147,6 @@
   </si>
   <si>
     <t>left</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>right</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -259,11 +255,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>少掌柜的，惠民药局的药料库起火啦。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>这火烧得蹊跷。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少掌柜的，惠民药局的药料库起火啦！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -809,7 +809,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>29</v>
@@ -828,7 +828,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -967,7 +967,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -978,7 +978,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>31</v>
@@ -1001,13 +1001,13 @@
         <v>30</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1021,15 +1021,15 @@
         <v>30</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1040,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>31</v>
@@ -1049,7 +1049,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1063,13 +1063,13 @@
         <v>30</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">

--- a/DataTables/DetailText/剧情/018库房失火.xlsx
+++ b/DataTables/DetailText/剧情/018库房失火.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84753520-9A8B-449C-8B9E-BF0873CB3701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E36ACC-88EF-402D-BA14-265DE11D65A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
   <si>
     <t>LineIndex</t>
   </si>
@@ -75,64 +61,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>night</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>current_scene</t>
@@ -266,16 +201,101 @@
     <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -289,7 +309,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -310,20 +330,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -337,8 +349,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,20 +387,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -397,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -420,45 +456,65 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -736,176 +792,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="24" customFormat="1">
+      <c r="A1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="P1" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="R1" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="S1" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="24" customFormat="1">
+      <c r="A2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="14" t="s">
+      <c r="D2" s="26">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="K2" s="26"/>
+      <c r="L2" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="25"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="9"/>
-      <c r="H3" s="13"/>
-      <c r="L3" s="17"/>
-      <c r="O3" s="10"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="9"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="9"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="9"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="9"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="13"/>
+      <c r="T2" s="27"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8"/>
+      <c r="H3" s="10"/>
+      <c r="L3" s="12"/>
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="8"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="8"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="C6" s="8"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="C7" s="8"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{24EE17A8-29F5-4B9A-87B7-6CF9FC788FA0}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{5A66DAB1-7690-4F3E-8A5D-9DD1A7EEC62A}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{ACDA4E82-C1CF-45C0-A17F-8906C16E28BD}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{AED2020A-1005-454D-A85C-D42BE3C5C9B8}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{0BFFD219-5DB0-4001-A970-6632A63A7DBF}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -913,166 +995,166 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
       <c r="G2" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>16</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H3" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H4" s="14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>31</v>
+        <v>6</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>16</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H6" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>30</v>
+        <v>6</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1084,7 +1166,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1096,7 +1178,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1108,7 +1190,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>

--- a/DataTables/DetailText/剧情/018库房失火.xlsx
+++ b/DataTables/DetailText/剧情/018库房失火.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E36ACC-88EF-402D-BA14-265DE11D65A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C685758-2F50-4CD7-96DB-1DE06ED683E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
   <si>
     <t>LineIndex</t>
   </si>
@@ -286,6 +297,10 @@
     <t>奖励心得</t>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
@@ -295,7 +310,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -309,7 +324,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -330,7 +345,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -433,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -512,9 +527,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -793,24 +811,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="24" customFormat="1">
+    <row r="1" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A1" s="17" t="s">
         <v>28</v>
       </c>
@@ -872,7 +890,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="24" customFormat="1">
+    <row r="2" spans="1:20" s="24" customFormat="1" ht="18">
       <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
@@ -994,21 +1012,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.125" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1033,8 +1051,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1051,8 +1072,9 @@
       <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1071,8 +1093,9 @@
       <c r="H3" s="14" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1091,8 +1114,9 @@
       <c r="H4" s="14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1113,8 +1137,9 @@
       <c r="H5" s="14" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1133,8 +1158,9 @@
       <c r="H6" s="14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1153,8 +1179,9 @@
       <c r="H7" s="16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1165,8 +1192,9 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1177,8 +1205,9 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1189,8 +1218,9 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1199,6 +1229,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
